--- a/TEST_RES.xlsx
+++ b/TEST_RES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python_projects\AI6127-DL-NLP-Assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91797E3C-74DA-4020-9702-48028D5D7C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6676A3-906C-43B3-9701-F490A4D2DAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0C47ED97-33DC-473C-B4B7-6D879BA33183}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t xml:space="preserve">TASK 1 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -517,6 +517,1016 @@
     <t>Epoch: 50 | Epoch Time: 0m 2s
 	Train Loss: 0.093 | Train Acc: 97.25%
 	 Val. Loss: 0.896 |  Val. Acc: 75.79%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TASK3 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPOCH 50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One-layer feed forward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two-layer feed forward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Three-layer feed-forward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bi-LSTM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LSTM </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 50 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.034 |  Val. Acc: 87.20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Loss: 0.330 | Test Acc: 86.21%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 01 | Epoch Time: 0m 2s
+	Train Loss: 0.372 | Train Acc: 84.29%
+	 Val. Loss: 0.363 |  Val. Acc: 84.60%
+Epoch: 02 | Epoch Time: 0m 2s
+	Train Loss: 0.280 | Train Acc: 88.72%
+	 Val. Loss: 0.338 |  Val. Acc: 85.74%
+Epoch: 03 | Epoch Time: 0m 2s
+	Train Loss: 0.216 | Train Acc: 92.10%
+	 Val. Loss: 0.306 |  Val. Acc: 87.82%
+Epoch: 04 | Epoch Time: 0m 2s
+	Train Loss: 0.173 | Train Acc: 93.90%
+	 Val. Loss: 0.330 |  Val. Acc: 87.25%
+Epoch: 05 | Epoch Time: 0m 2s
+	Train Loss: 0.146 | Train Acc: 95.45%
+	 Val. Loss: 0.325 |  Val. Acc: 87.94%
+Epoch: 06 | Epoch Time: 0m 2s
+	Train Loss: 0.119 | Train Acc: 96.82%
+	 Val. Loss: 0.347 |  Val. Acc: 87.86%
+Epoch: 07 | Epoch Time: 0m 2s
+	Train Loss: 0.089 | Train Acc: 97.59%
+	 Val. Loss: 0.403 |  Val. Acc: 87.15%
+Epoch: 08 | Epoch Time: 0m 2s
+	Train Loss: 0.097 | Train Acc: 97.93%
+	 Val. Loss: 0.432 |  Val. Acc: 87.47%
+Epoch: 09 | Epoch Time: 0m 2s
+	Train Loss: 0.064 | Train Acc: 98.91%
+	 Val. Loss: 0.420 |  Val. Acc: 87.86%
+Epoch: 10 | Epoch Time: 0m 2s
+	Train Loss: 0.051 | Train Acc: 99.06%
+	 Val. Loss: 0.465 |  Val. Acc: 87.22%
+Epoch: 11 | Epoch Time: 0m 2s
+	Train Loss: 0.056 | Train Acc: 99.18%
+	 Val. Loss: 0.507 |  Val. Acc: 86.97%
+Epoch: 12 | Epoch Time: 0m 2s
+	Train Loss: 0.040 | Train Acc: 99.25%
+	 Val. Loss: 0.500 |  Val. Acc: 87.26%
+Epoch: 13 | Epoch Time: 0m 3s
+	Train Loss: 0.061 | Train Acc: 99.36%
+	 Val. Loss: 0.500 |  Val. Acc: 87.54%
+Epoch: 14 | Epoch Time: 0m 3s
+	Train Loss: 0.020 | Train Acc: 99.67%
+	 Val. Loss: 0.516 |  Val. Acc: 87.57%
+Epoch: 15 | Epoch Time: 0m 3s
+	Train Loss: 0.014 | Train Acc: 99.58%
+	 Val. Loss: 0.596 |  Val. Acc: 86.80%
+Epoch: 16 | Epoch Time: 0m 3s
+	Train Loss: 0.040 | Train Acc: 99.62%
+	 Val. Loss: 0.565 |  Val. Acc: 87.53%
+Epoch: 17 | Epoch Time: 0m 2s
+	Train Loss: 0.024 | Train Acc: 99.53%
+	 Val. Loss: 0.603 |  Val. Acc: 87.29%
+Epoch: 18 | Epoch Time: 0m 3s
+	Train Loss: 0.043 | Train Acc: 99.45%
+	 Val. Loss: 0.613 |  Val. Acc: 86.95%
+Epoch: 19 | Epoch Time: 0m 3s
+	Train Loss: 0.028 | Train Acc: 99.58%
+	 Val. Loss: 0.613 |  Val. Acc: 87.45%
+Epoch: 20 | Epoch Time: 0m 2s
+	Train Loss: 0.003 | Train Acc: 99.99%
+	 Val. Loss: 0.631 |  Val. Acc: 87.57%
+Epoch: 21 | Epoch Time: 0m 3s
+	Train Loss: 0.006 | Train Acc: 99.89%
+	 Val. Loss: 0.667 |  Val. Acc: 87.29%
+Epoch: 22 | Epoch Time: 0m 3s
+	Train Loss: 0.020 | Train Acc: 99.63%
+	 Val. Loss: 0.672 |  Val. Acc: 87.33%
+Epoch: 23 | Epoch Time: 0m 3s
+	Train Loss: 0.012 | Train Acc: 99.65%
+	 Val. Loss: 0.728 |  Val. Acc: 86.84%
+Epoch: 24 | Epoch Time: 0m 3s
+	Train Loss: 0.034 | Train Acc: 99.69%
+	 Val. Loss: 0.701 |  Val. Acc: 87.32%
+Epoch: 25 | Epoch Time: 0m 3s
+	Train Loss: 0.001 | Train Acc: 99.99%
+	 Val. Loss: 0.714 |  Val. Acc: 87.23%
+Epoch: 26 | Epoch Time: 0m 3s
+	Train Loss: 0.001 | Train Acc: 100.00%
+	 Val. Loss: 0.723 |  Val. Acc: 87.28%
+Epoch: 27 | Epoch Time: 0m 3s
+	Train Loss: 0.001 | Train Acc: 100.00%
+	 Val. Loss: 0.733 |  Val. Acc: 87.25%
+Epoch: 28 | Epoch Time: 0m 3s
+	Train Loss: 0.001 | Train Acc: 99.99%
+	 Val. Loss: 0.754 |  Val. Acc: 87.39%
+Epoch: 29 | Epoch Time: 0m 3s
+	Train Loss: 0.001 | Train Acc: 99.98%
+	 Val. Loss: 0.763 |  Val. Acc: 87.36%
+Epoch: 30 | Epoch Time: 0m 3s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.777 |  Val. Acc: 87.28%
+Epoch: 31 | Epoch Time: 0m 3s
+	Train Loss: 0.001 | Train Acc: 100.00%
+	 Val. Loss: 0.794 |  Val. Acc: 87.23%
+Epoch: 32 | Epoch Time: 0m 2s
+	Train Loss: 0.041 | Train Acc: 99.39%
+	 Val. Loss: 0.918 |  Val. Acc: 86.82%
+Epoch: 33 | Epoch Time: 0m 3s
+	Train Loss: 0.086 | Train Acc: 99.28%
+	 Val. Loss: 0.896 |  Val. Acc: 87.19%
+Epoch: 34 | Epoch Time: 0m 3s
+	Train Loss: 0.027 | Train Acc: 99.49%
+	 Val. Loss: 0.909 |  Val. Acc: 86.96%
+Epoch: 35 | Epoch Time: 0m 3s
+	Train Loss: 0.024 | Train Acc: 99.66%
+	 Val. Loss: 0.880 |  Val. Acc: 87.11%
+Epoch: 36 | Epoch Time: 0m 3s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.884 |  Val. Acc: 87.23%
+Epoch: 37 | Epoch Time: 0m 3s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.888 |  Val. Acc: 87.19%
+Epoch: 38 | Epoch Time: 0m 3s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.892 |  Val. Acc: 87.16%
+Epoch: 39 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.896 |  Val. Acc: 87.12%
+Epoch: 40 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.899 |  Val. Acc: 87.11%
+Epoch: 41 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.910 |  Val. Acc: 87.17%
+Epoch: 42 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.920 |  Val. Acc: 87.13%
+Epoch: 43 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.930 |  Val. Acc: 87.04%
+Epoch: 44 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.946 |  Val. Acc: 87.05%
+Epoch: 45 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.959 |  Val. Acc: 87.11%
+Epoch: 46 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.973 |  Val. Acc: 87.09%
+Epoch: 47 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.988 |  Val. Acc: 87.07%
+Epoch: 48 | Epoch Time: 0m 1s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.002 |  Val. Acc: 87.12%
+Epoch: 49 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.016 |  Val. Acc: 87.13%
+Epoch: 50 | Epoch Time: 0m 2s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.034 |  Val. Acc: 87.20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 50 | Epoch Time: 0m 3s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.682 |  Val. Acc: 86.90%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Loss: 0.360 | Test Acc: 85.03%</t>
+  </si>
+  <si>
+    <t>Epoch: 01 | Epoch Time: 0m 2s
+	Train Loss: 0.546 | Train Acc: 71.80%
+	 Val. Loss: 0.439 |  Val. Acc: 80.16%
+Epoch: 02 | Epoch Time: 0m 2s
+	Train Loss: 0.356 | Train Acc: 84.45%
+	 Val. Loss: 0.354 |  Val. Acc: 84.69%
+Epoch: 03 | Epoch Time: 0m 2s
+	Train Loss: 0.259 | Train Acc: 89.54%
+	 Val. Loss: 0.352 |  Val. Acc: 85.52%
+Epoch: 04 | Epoch Time: 0m 2s
+	Train Loss: 0.204 | Train Acc: 92.69%
+	 Val. Loss: 0.367 |  Val. Acc: 85.07%
+Epoch: 05 | Epoch Time: 0m 2s
+	Train Loss: 0.137 | Train Acc: 95.15%
+	 Val. Loss: 0.364 |  Val. Acc: 87.01%
+Epoch: 06 | Epoch Time: 0m 2s
+	Train Loss: 0.090 | Train Acc: 97.01%
+	 Val. Loss: 0.448 |  Val. Acc: 86.94%
+Epoch: 07 | Epoch Time: 0m 2s
+	Train Loss: 0.066 | Train Acc: 97.99%
+	 Val. Loss: 0.486 |  Val. Acc: 87.12%
+Epoch: 08 | Epoch Time: 0m 2s
+	Train Loss: 0.038 | Train Acc: 98.84%
+	 Val. Loss: 0.561 |  Val. Acc: 87.12%
+Epoch: 09 | Epoch Time: 0m 2s
+	Train Loss: 0.046 | Train Acc: 98.48%
+	 Val. Loss: 0.593 |  Val. Acc: 87.06%
+Epoch: 10 | Epoch Time: 0m 2s
+	Train Loss: 0.029 | Train Acc: 99.12%
+	 Val. Loss: 0.700 |  Val. Acc: 86.92%
+Epoch: 11 | Epoch Time: 0m 1s
+	Train Loss: 0.055 | Train Acc: 98.09%
+	 Val. Loss: 0.761 |  Val. Acc: 86.66%
+Epoch: 12 | Epoch Time: 0m 2s
+	Train Loss: 0.014 | Train Acc: 99.65%
+	 Val. Loss: 0.837 |  Val. Acc: 87.04%
+Epoch: 13 | Epoch Time: 0m 2s
+	Train Loss: 0.041 | Train Acc: 98.75%
+	 Val. Loss: 0.828 |  Val. Acc: 87.15%
+Epoch: 14 | Epoch Time: 0m 2s
+	Train Loss: 0.013 | Train Acc: 99.31%
+	 Val. Loss: 0.918 |  Val. Acc: 86.68%
+Epoch: 15 | Epoch Time: 0m 2s
+	Train Loss: 0.017 | Train Acc: 99.46%
+	 Val. Loss: 0.960 |  Val. Acc: 87.14%
+Epoch: 16 | Epoch Time: 0m 2s
+	Train Loss: 0.009 | Train Acc: 99.60%
+	 Val. Loss: 1.018 |  Val. Acc: 86.94%
+Epoch: 17 | Epoch Time: 0m 2s
+	Train Loss: 0.006 | Train Acc: 99.92%
+	 Val. Loss: 1.124 |  Val. Acc: 87.36%
+Epoch: 18 | Epoch Time: 0m 2s
+	Train Loss: 0.030 | Train Acc: 99.18%
+	 Val. Loss: 0.929 |  Val. Acc: 87.16%
+Epoch: 19 | Epoch Time: 0m 2s
+	Train Loss: 0.011 | Train Acc: 99.52%
+	 Val. Loss: 0.997 |  Val. Acc: 87.24%
+Epoch: 20 | Epoch Time: 0m 2s
+	Train Loss: 0.022 | Train Acc: 99.36%
+	 Val. Loss: 0.950 |  Val. Acc: 86.96%
+Epoch: 21 | Epoch Time: 0m 2s
+	Train Loss: 0.009 | Train Acc: 99.50%
+	 Val. Loss: 1.088 |  Val. Acc: 86.75%
+Epoch: 22 | Epoch Time: 0m 2s
+	Train Loss: 0.023 | Train Acc: 99.16%
+	 Val. Loss: 1.122 |  Val. Acc: 86.39%
+Epoch: 23 | Epoch Time: 0m 2s
+	Train Loss: 0.018 | Train Acc: 99.37%
+	 Val. Loss: 1.219 |  Val. Acc: 86.97%
+Epoch: 24 | Epoch Time: 0m 2s
+	Train Loss: 0.021 | Train Acc: 99.57%
+	 Val. Loss: 1.177 |  Val. Acc: 86.58%
+Epoch: 25 | Epoch Time: 0m 2s
+	Train Loss: 0.020 | Train Acc: 99.26%
+	 Val. Loss: 0.987 |  Val. Acc: 86.59%
+Epoch: 26 | Epoch Time: 0m 2s
+	Train Loss: 0.018 | Train Acc: 99.24%
+	 Val. Loss: 1.108 |  Val. Acc: 86.88%
+Epoch: 27 | Epoch Time: 0m 2s
+	Train Loss: 0.010 | Train Acc: 99.42%
+	 Val. Loss: 1.255 |  Val. Acc: 86.74%
+Epoch: 28 | Epoch Time: 0m 2s
+	Train Loss: 0.015 | Train Acc: 99.55%
+	 Val. Loss: 1.193 |  Val. Acc: 87.33%
+Epoch: 29 | Epoch Time: 0m 2s
+	Train Loss: 0.020 | Train Acc: 99.33%
+	 Val. Loss: 1.241 |  Val. Acc: 86.97%
+Epoch: 30 | Epoch Time: 0m 2s
+	Train Loss: 0.008 | Train Acc: 99.54%
+	 Val. Loss: 1.401 |  Val. Acc: 86.59%
+Epoch: 31 | Epoch Time: 0m 2s
+	Train Loss: 0.007 | Train Acc: 99.59%
+	 Val. Loss: 1.340 |  Val. Acc: 86.78%
+Epoch: 32 | Epoch Time: 0m 2s
+	Train Loss: 0.005 | Train Acc: 99.80%
+	 Val. Loss: 1.382 |  Val. Acc: 87.31%
+Epoch: 33 | Epoch Time: 0m 2s
+	Train Loss: 0.014 | Train Acc: 99.44%
+	 Val. Loss: 1.230 |  Val. Acc: 86.51%
+Epoch: 34 | Epoch Time: 0m 3s
+	Train Loss: 0.011 | Train Acc: 99.65%
+	 Val. Loss: 1.179 |  Val. Acc: 86.76%
+Epoch: 35 | Epoch Time: 0m 3s
+	Train Loss: 0.008 | Train Acc: 99.64%
+	 Val. Loss: 1.333 |  Val. Acc: 86.82%
+Epoch: 36 | Epoch Time: 0m 3s
+	Train Loss: 0.012 | Train Acc: 99.33%
+	 Val. Loss: 1.412 |  Val. Acc: 87.04%
+Epoch: 37 | Epoch Time: 0m 3s
+	Train Loss: 0.006 | Train Acc: 99.64%
+	 Val. Loss: 1.514 |  Val. Acc: 87.16%
+Epoch: 38 | Epoch Time: 0m 3s
+	Train Loss: 0.036 | Train Acc: 99.16%
+	 Val. Loss: 1.307 |  Val. Acc: 86.36%
+Epoch: 39 | Epoch Time: 0m 3s
+	Train Loss: 0.047 | Train Acc: 99.01%
+	 Val. Loss: 1.080 |  Val. Acc: 87.04%
+Epoch: 40 | Epoch Time: 0m 3s
+	Train Loss: 0.057 | Train Acc: 99.38%
+	 Val. Loss: 0.866 |  Val. Acc: 87.00%
+Epoch: 41 | Epoch Time: 0m 3s
+	Train Loss: 0.006 | Train Acc: 99.81%
+	 Val. Loss: 1.077 |  Val. Acc: 86.92%
+Epoch: 42 | Epoch Time: 0m 3s
+	Train Loss: 0.028 | Train Acc: 99.27%
+	 Val. Loss: 1.201 |  Val. Acc: 87.19%
+Epoch: 43 | Epoch Time: 0m 2s
+	Train Loss: 0.004 | Train Acc: 99.90%
+	 Val. Loss: 1.260 |  Val. Acc: 87.04%
+Epoch: 44 | Epoch Time: 0m 3s
+	Train Loss: 0.019 | Train Acc: 99.58%
+	 Val. Loss: 1.276 |  Val. Acc: 87.09%
+Epoch: 45 | Epoch Time: 0m 3s
+	Train Loss: 0.006 | Train Acc: 99.69%
+	 Val. Loss: 1.388 |  Val. Acc: 87.04%
+Epoch: 46 | Epoch Time: 0m 3s
+	Train Loss: 0.001 | Train Acc: 99.96%
+	 Val. Loss: 1.440 |  Val. Acc: 87.20%
+Epoch: 47 | Epoch Time: 0m 3s
+	Train Loss: 0.012 | Train Acc: 99.79%
+	 Val. Loss: 1.516 |  Val. Acc: 86.82%
+Epoch: 48 | Epoch Time: 0m 3s
+	Train Loss: 0.012 | Train Acc: 99.60%
+	 Val. Loss: 1.547 |  Val. Acc: 87.11%
+Epoch: 49 | Epoch Time: 0m 3s
+	Train Loss: 0.002 | Train Acc: 99.98%
+	 Val. Loss: 1.645 |  Val. Acc: 87.11%
+Epoch: 50 | Epoch Time: 0m 3s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.682 |  Val. Acc: 86.90%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 50 | Epoch Time: 0m 2s
+	Train Loss: 0.005 | Train Acc: 99.90%
+	 Val. Loss: 1.333 |  Val. Acc: 87.01%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Loss: 0.354 | Test Acc: 85.71%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The model has 2,761,401 trainable parameters
+Epoch: 01 | Epoch Time: 0m 2s
+	Train Loss: 0.544 | Train Acc: 71.73%
+	 Val. Loss: 0.429 |  Val. Acc: 80.26%
+Epoch: 02 | Epoch Time: 0m 2s
+	Train Loss: 0.361 | Train Acc: 84.44%
+	 Val. Loss: 0.363 |  Val. Acc: 84.62%
+Epoch: 03 | Epoch Time: 0m 2s
+	Train Loss: 0.269 | Train Acc: 89.27%
+	 Val. Loss: 0.357 |  Val. Acc: 85.60%
+Epoch: 04 | Epoch Time: 0m 2s
+	Train Loss: 0.220 | Train Acc: 92.38%
+	 Val. Loss: 0.343 |  Val. Acc: 86.64%
+Epoch: 05 | Epoch Time: 0m 2s
+	Train Loss: 0.153 | Train Acc: 94.62%
+	 Val. Loss: 0.346 |  Val. Acc: 88.08%
+Epoch: 06 | Epoch Time: 0m 2s
+	Train Loss: 0.111 | Train Acc: 96.21%
+	 Val. Loss: 0.457 |  Val. Acc: 86.90%
+Epoch: 07 | Epoch Time: 0m 2s
+	Train Loss: 0.075 | Train Acc: 97.61%
+	 Val. Loss: 0.463 |  Val. Acc: 87.81%
+Epoch: 08 | Epoch Time: 0m 2s
+	Train Loss: 0.049 | Train Acc: 98.47%
+	 Val. Loss: 0.529 |  Val. Acc: 86.69%
+Epoch: 09 | Epoch Time: 0m 2s
+	Train Loss: 0.054 | Train Acc: 98.22%
+	 Val. Loss: 0.647 |  Val. Acc: 87.20%
+Epoch: 10 | Epoch Time: 0m 2s
+	Train Loss: 0.030 | Train Acc: 99.03%
+	 Val. Loss: 0.882 |  Val. Acc: 86.11%
+Epoch: 11 | Epoch Time: 0m 2s
+	Train Loss: 0.049 | Train Acc: 98.18%
+	 Val. Loss: 0.594 |  Val. Acc: 86.94%
+Epoch: 12 | Epoch Time: 0m 2s
+	Train Loss: 0.024 | Train Acc: 99.03%
+	 Val. Loss: 0.687 |  Val. Acc: 86.79%
+Epoch: 13 | Epoch Time: 0m 2s
+	Train Loss: 0.022 | Train Acc: 99.23%
+	 Val. Loss: 0.754 |  Val. Acc: 87.23%
+Epoch: 14 | Epoch Time: 0m 2s
+	Train Loss: 0.015 | Train Acc: 99.27%
+	 Val. Loss: 0.962 |  Val. Acc: 85.91%
+Epoch: 15 | Epoch Time: 0m 2s
+	Train Loss: 0.019 | Train Acc: 99.23%
+	 Val. Loss: 0.999 |  Val. Acc: 86.99%
+Epoch: 16 | Epoch Time: 0m 2s
+	Train Loss: 0.016 | Train Acc: 99.11%
+	 Val. Loss: 0.733 |  Val. Acc: 87.28%
+Epoch: 17 | Epoch Time: 0m 1s
+	Train Loss: 0.016 | Train Acc: 99.44%
+	 Val. Loss: 0.940 |  Val. Acc: 87.36%
+Epoch: 18 | Epoch Time: 0m 2s
+	Train Loss: 0.035 | Train Acc: 99.05%
+	 Val. Loss: 1.041 |  Val. Acc: 87.53%
+Epoch: 19 | Epoch Time: 0m 1s
+	Train Loss: 0.068 | Train Acc: 98.94%
+	 Val. Loss: 0.813 |  Val. Acc: 87.44%
+Epoch: 20 | Epoch Time: 0m 2s
+	Train Loss: 0.010 | Train Acc: 99.42%
+	 Val. Loss: 0.974 |  Val. Acc: 87.16%
+Epoch: 21 | Epoch Time: 0m 2s
+	Train Loss: 0.014 | Train Acc: 99.58%
+	 Val. Loss: 0.884 |  Val. Acc: 87.20%
+Epoch: 22 | Epoch Time: 0m 2s
+	Train Loss: 0.007 | Train Acc: 99.62%
+	 Val. Loss: 1.015 |  Val. Acc: 87.61%
+Epoch: 23 | Epoch Time: 0m 2s
+	Train Loss: 0.008 | Train Acc: 99.50%
+	 Val. Loss: 1.094 |  Val. Acc: 87.41%
+Epoch: 24 | Epoch Time: 0m 2s
+	Train Loss: 0.018 | Train Acc: 99.38%
+	 Val. Loss: 0.848 |  Val. Acc: 87.65%
+Epoch: 25 | Epoch Time: 0m 2s
+	Train Loss: 0.008 | Train Acc: 99.61%
+	 Val. Loss: 1.097 |  Val. Acc: 87.03%
+Epoch: 26 | Epoch Time: 0m 2s
+	Train Loss: 0.006 | Train Acc: 99.79%
+	 Val. Loss: 1.253 |  Val. Acc: 87.56%
+Epoch: 27 | Epoch Time: 0m 2s
+	Train Loss: 0.027 | Train Acc: 99.34%
+	 Val. Loss: 0.807 |  Val. Acc: 87.51%
+Epoch: 28 | Epoch Time: 0m 2s
+	Train Loss: 0.011 | Train Acc: 99.33%
+	 Val. Loss: 0.962 |  Val. Acc: 87.25%
+Epoch: 29 | Epoch Time: 0m 2s
+	Train Loss: 0.007 | Train Acc: 99.51%
+	 Val. Loss: 1.116 |  Val. Acc: 87.60%
+Epoch: 30 | Epoch Time: 0m 2s
+	Train Loss: 0.046 | Train Acc: 99.38%
+	 Val. Loss: 1.015 |  Val. Acc: 87.54%
+Epoch: 31 | Epoch Time: 0m 2s
+	Train Loss: 0.045 | Train Acc: 99.50%
+	 Val. Loss: 0.825 |  Val. Acc: 86.28%
+Epoch: 32 | Epoch Time: 0m 2s
+	Train Loss: 0.017 | Train Acc: 99.32%
+	 Val. Loss: 1.036 |  Val. Acc: 87.33%
+Epoch: 33 | Epoch Time: 0m 2s
+	Train Loss: 0.065 | Train Acc: 99.11%
+	 Val. Loss: 0.670 |  Val. Acc: 87.74%
+Epoch: 34 | Epoch Time: 0m 2s
+	Train Loss: 0.016 | Train Acc: 99.59%
+	 Val. Loss: 0.708 |  Val. Acc: 87.33%
+Epoch: 35 | Epoch Time: 0m 2s
+	Train Loss: 0.014 | Train Acc: 99.71%
+	 Val. Loss: 1.088 |  Val. Acc: 87.61%
+Epoch: 36 | Epoch Time: 0m 2s
+	Train Loss: 0.010 | Train Acc: 99.56%
+	 Val. Loss: 1.144 |  Val. Acc: 87.41%
+Epoch: 37 | Epoch Time: 0m 2s
+	Train Loss: 0.010 | Train Acc: 99.50%
+	 Val. Loss: 1.209 |  Val. Acc: 87.24%
+Epoch: 38 | Epoch Time: 0m 2s
+	Train Loss: 0.008 | Train Acc: 99.56%
+	 Val. Loss: 1.277 |  Val. Acc: 87.46%
+Epoch: 39 | Epoch Time: 0m 2s
+	Train Loss: 0.014 | Train Acc: 99.61%
+	 Val. Loss: 0.954 |  Val. Acc: 87.29%
+Epoch: 40 | Epoch Time: 0m 2s
+	Train Loss: 0.008 | Train Acc: 99.74%
+	 Val. Loss: 1.133 |  Val. Acc: 86.94%
+Epoch: 41 | Epoch Time: 0m 2s
+	Train Loss: 0.016 | Train Acc: 99.50%
+	 Val. Loss: 0.897 |  Val. Acc: 86.17%
+Epoch: 42 | Epoch Time: 0m 2s
+	Train Loss: 0.014 | Train Acc: 99.50%
+	 Val. Loss: 1.228 |  Val. Acc: 87.45%
+Epoch: 43 | Epoch Time: 0m 2s
+	Train Loss: 0.006 | Train Acc: 99.92%
+	 Val. Loss: 1.256 |  Val. Acc: 87.22%
+Epoch: 44 | Epoch Time: 0m 2s
+	Train Loss: 0.015 | Train Acc: 99.54%
+	 Val. Loss: 0.946 |  Val. Acc: 85.82%
+Epoch: 45 | Epoch Time: 0m 2s
+	Train Loss: 0.020 | Train Acc: 99.39%
+	 Val. Loss: 1.072 |  Val. Acc: 87.32%
+Epoch: 46 | Epoch Time: 0m 2s
+	Train Loss: 0.005 | Train Acc: 99.87%
+	 Val. Loss: 1.410 |  Val. Acc: 87.01%
+Epoch: 47 | Epoch Time: 0m 2s
+	Train Loss: 0.013 | Train Acc: 99.45%
+	 Val. Loss: 1.412 |  Val. Acc: 87.25%
+Epoch: 48 | Epoch Time: 0m 2s
+	Train Loss: 0.005 | Train Acc: 99.69%
+	 Val. Loss: 1.525 |  Val. Acc: 87.33%
+Epoch: 49 | Epoch Time: 0m 2s
+	Train Loss: 0.001 | Train Acc: 99.97%
+	 Val. Loss: 1.633 |  Val. Acc: 87.00%
+Epoch: 50 | Epoch Time: 0m 2s
+	Train Loss: 0.005 | Train Acc: 99.90%
+	 Val. Loss: 1.333 |  Val. Acc: 87.01%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">CNN - 3 feature maps </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 50 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.575 |  Val. Acc: 89.03%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Loss: 0.284 | Test Acc: 88.14%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 01 | Epoch Time: 0m 7s
+	Train Loss: 0.505 | Train Acc: 75.53%
+	 Val. Loss: 0.401 |  Val. Acc: 82.04%
+Epoch: 02 | Epoch Time: 0m 7s
+	Train Loss: 0.311 | Train Acc: 87.59%
+	 Val. Loss: 0.317 |  Val. Acc: 86.56%
+Epoch: 03 | Epoch Time: 0m 7s
+	Train Loss: 0.217 | Train Acc: 92.17%
+	 Val. Loss: 0.296 |  Val. Acc: 87.11%
+Epoch: 04 | Epoch Time: 0m 7s
+	Train Loss: 0.150 | Train Acc: 95.40%
+	 Val. Loss: 0.288 |  Val. Acc: 87.65%
+Epoch: 05 | Epoch Time: 0m 6s
+	Train Loss: 0.090 | Train Acc: 98.25%
+	 Val. Loss: 0.286 |  Val. Acc: 87.94%
+Epoch: 06 | Epoch Time: 0m 6s
+	Train Loss: 0.052 | Train Acc: 99.55%
+	 Val. Loss: 0.297 |  Val. Acc: 88.51%
+Epoch: 07 | Epoch Time: 0m 6s
+	Train Loss: 0.029 | Train Acc: 99.93%
+	 Val. Loss: 0.304 |  Val. Acc: 88.46%
+Epoch: 08 | Epoch Time: 0m 6s
+	Train Loss: 0.017 | Train Acc: 99.98%
+	 Val. Loss: 0.311 |  Val. Acc: 88.58%
+Epoch: 09 | Epoch Time: 0m 7s
+	Train Loss: 0.011 | Train Acc: 100.00%
+	 Val. Loss: 0.322 |  Val. Acc: 88.50%
+Epoch: 10 | Epoch Time: 0m 6s
+	Train Loss: 0.007 | Train Acc: 100.00%
+	 Val. Loss: 0.331 |  Val. Acc: 88.54%
+Epoch: 11 | Epoch Time: 0m 6s
+	Train Loss: 0.005 | Train Acc: 100.00%
+	 Val. Loss: 0.338 |  Val. Acc: 88.59%
+Epoch: 12 | Epoch Time: 0m 6s
+	Train Loss: 0.004 | Train Acc: 100.00%
+	 Val. Loss: 0.348 |  Val. Acc: 88.47%
+Epoch: 13 | Epoch Time: 0m 7s
+	Train Loss: 0.003 | Train Acc: 100.00%
+	 Val. Loss: 0.355 |  Val. Acc: 88.64%
+Epoch: 14 | Epoch Time: 0m 6s
+	Train Loss: 0.002 | Train Acc: 100.00%
+	 Val. Loss: 0.364 |  Val. Acc: 88.68%
+Epoch: 15 | Epoch Time: 0m 6s
+	Train Loss: 0.002 | Train Acc: 100.00%
+	 Val. Loss: 0.371 |  Val. Acc: 88.67%
+Epoch: 16 | Epoch Time: 0m 7s
+	Train Loss: 0.001 | Train Acc: 100.00%
+	 Val. Loss: 0.377 |  Val. Acc: 88.68%
+Epoch: 17 | Epoch Time: 0m 6s
+	Train Loss: 0.001 | Train Acc: 100.00%
+	 Val. Loss: 0.383 |  Val. Acc: 88.82%
+Epoch: 18 | Epoch Time: 0m 6s
+	Train Loss: 0.001 | Train Acc: 100.00%
+	 Val. Loss: 0.390 |  Val. Acc: 88.74%
+Epoch: 19 | Epoch Time: 0m 6s
+	Train Loss: 0.001 | Train Acc: 100.00%
+	 Val. Loss: 0.398 |  Val. Acc: 88.62%
+Epoch: 20 | Epoch Time: 0m 6s
+	Train Loss: 0.001 | Train Acc: 100.00%
+	 Val. Loss: 0.407 |  Val. Acc: 88.64%
+Epoch: 21 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.411 |  Val. Acc: 88.68%
+Epoch: 22 | Epoch Time: 0m 5s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.415 |  Val. Acc: 88.84%
+Epoch: 23 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.422 |  Val. Acc: 88.84%
+Epoch: 24 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.428 |  Val. Acc: 88.75%
+Epoch: 25 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.434 |  Val. Acc: 88.74%
+Epoch: 26 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.439 |  Val. Acc: 88.79%
+Epoch: 27 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.445 |  Val. Acc: 88.78%
+Epoch: 28 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.454 |  Val. Acc: 88.72%
+Epoch: 29 | Epoch Time: 0m 5s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.459 |  Val. Acc: 88.76%
+Epoch: 30 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.464 |  Val. Acc: 88.78%
+Epoch: 31 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.471 |  Val. Acc: 88.78%
+Epoch: 32 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.475 |  Val. Acc: 88.79%
+Epoch: 33 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.479 |  Val. Acc: 88.96%
+Epoch: 34 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.486 |  Val. Acc: 88.78%
+Epoch: 35 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.490 |  Val. Acc: 88.91%
+Epoch: 36 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.498 |  Val. Acc: 88.88%
+Epoch: 37 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.503 |  Val. Acc: 88.88%
+Epoch: 38 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.508 |  Val. Acc: 88.87%
+Epoch: 39 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.514 |  Val. Acc: 88.93%
+Epoch: 40 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.521 |  Val. Acc: 88.96%
+Epoch: 41 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.524 |  Val. Acc: 88.92%
+Epoch: 42 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.530 |  Val. Acc: 88.92%
+Epoch: 43 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.535 |  Val. Acc: 88.88%
+Epoch: 44 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.541 |  Val. Acc: 88.96%
+Epoch: 45 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.547 |  Val. Acc: 89.00%
+Epoch: 46 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.553 |  Val. Acc: 88.96%
+Epoch: 47 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.558 |  Val. Acc: 88.96%
+Epoch: 48 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.564 |  Val. Acc: 89.00%
+Epoch: 49 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.567 |  Val. Acc: 88.88%
+Epoch: 50 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.575 |  Val. Acc: 89.03%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 50 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.489 |  Val. Acc: 87.11%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Loss: 0.345 | Test Acc: 86.00%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 01 | Epoch Time: 0m 6s
+	Train Loss: 0.644 | Train Acc: 62.52%
+	 Val. Loss: 0.588 |  Val. Acc: 69.04%
+Epoch: 02 | Epoch Time: 0m 6s
+	Train Loss: 0.632 | Train Acc: 64.74%
+	 Val. Loss: 0.652 |  Val. Acc: 61.80%
+Epoch: 03 | Epoch Time: 0m 6s
+	Train Loss: 0.554 | Train Acc: 71.41%
+	 Val. Loss: 0.479 |  Val. Acc: 77.89%
+Epoch: 04 | Epoch Time: 0m 6s
+	Train Loss: 0.345 | Train Acc: 85.35%
+	 Val. Loss: 0.348 |  Val. Acc: 85.00%
+Epoch: 05 | Epoch Time: 0m 6s
+	Train Loss: 0.236 | Train Acc: 90.96%
+	 Val. Loss: 0.327 |  Val. Acc: 86.51%
+Epoch: 06 | Epoch Time: 0m 6s
+	Train Loss: 0.161 | Train Acc: 94.38%
+	 Val. Loss: 0.344 |  Val. Acc: 87.53%
+Epoch: 07 | Epoch Time: 0m 6s
+	Train Loss: 0.105 | Train Acc: 96.84%
+	 Val. Loss: 0.408 |  Val. Acc: 87.12%
+Epoch: 08 | Epoch Time: 0m 6s
+	Train Loss: 0.069 | Train Acc: 98.03%
+	 Val. Loss: 0.422 |  Val. Acc: 87.52%
+Epoch: 09 | Epoch Time: 0m 6s
+	Train Loss: 0.049 | Train Acc: 98.65%
+	 Val. Loss: 0.443 |  Val. Acc: 86.90%
+Epoch: 10 | Epoch Time: 0m 6s
+	Train Loss: 0.035 | Train Acc: 99.11%
+	 Val. Loss: 0.536 |  Val. Acc: 87.25%
+Epoch: 11 | Epoch Time: 0m 6s
+	Train Loss: 0.019 | Train Acc: 99.57%
+	 Val. Loss: 0.603 |  Val. Acc: 86.50%
+Epoch: 12 | Epoch Time: 0m 6s
+	Train Loss: 0.015 | Train Acc: 99.60%
+	 Val. Loss: 0.538 |  Val. Acc: 86.07%
+Epoch: 13 | Epoch Time: 0m 6s
+	Train Loss: 0.016 | Train Acc: 99.58%
+	 Val. Loss: 0.657 |  Val. Acc: 86.60%
+Epoch: 14 | Epoch Time: 0m 6s
+	Train Loss: 0.013 | Train Acc: 99.66%
+	 Val. Loss: 0.679 |  Val. Acc: 86.27%
+Epoch: 15 | Epoch Time: 0m 6s
+	Train Loss: 0.007 | Train Acc: 99.85%
+	 Val. Loss: 0.736 |  Val. Acc: 86.99%
+Epoch: 16 | Epoch Time: 0m 6s
+	Train Loss: 0.004 | Train Acc: 99.91%
+	 Val. Loss: 0.811 |  Val. Acc: 85.44%
+Epoch: 17 | Epoch Time: 0m 6s
+	Train Loss: 0.013 | Train Acc: 99.67%
+	 Val. Loss: 0.690 |  Val. Acc: 86.92%
+Epoch: 18 | Epoch Time: 0m 6s
+	Train Loss: 0.007 | Train Acc: 99.81%
+	 Val. Loss: 0.799 |  Val. Acc: 85.39%
+Epoch: 19 | Epoch Time: 0m 6s
+	Train Loss: 0.037 | Train Acc: 98.53%
+	 Val. Loss: 0.637 |  Val. Acc: 86.38%
+Epoch: 20 | Epoch Time: 0m 6s
+	Train Loss: 0.007 | Train Acc: 99.79%
+	 Val. Loss: 0.736 |  Val. Acc: 86.74%
+Epoch: 21 | Epoch Time: 0m 6s
+	Train Loss: 0.005 | Train Acc: 99.83%
+	 Val. Loss: 0.738 |  Val. Acc: 87.32%
+Epoch: 22 | Epoch Time: 0m 6s
+	Train Loss: 0.003 | Train Acc: 99.93%
+	 Val. Loss: 0.762 |  Val. Acc: 86.94%
+Epoch: 23 | Epoch Time: 0m 6s
+	Train Loss: 0.001 | Train Acc: 99.98%
+	 Val. Loss: 0.891 |  Val. Acc: 87.33%
+Epoch: 24 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.920 |  Val. Acc: 87.25%
+Epoch: 25 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.966 |  Val. Acc: 87.35%
+Epoch: 26 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.999 |  Val. Acc: 87.24%
+Epoch: 27 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.025 |  Val. Acc: 87.27%
+Epoch: 28 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.055 |  Val. Acc: 87.25%
+Epoch: 29 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.076 |  Val. Acc: 87.20%
+Epoch: 30 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.102 |  Val. Acc: 87.28%
+Epoch: 31 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.122 |  Val. Acc: 87.27%
+Epoch: 32 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.146 |  Val. Acc: 87.25%
+Epoch: 33 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.164 |  Val. Acc: 87.25%
+Epoch: 34 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.185 |  Val. Acc: 87.25%
+Epoch: 35 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.205 |  Val. Acc: 87.29%
+Epoch: 36 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.225 |  Val. Acc: 87.33%
+Epoch: 37 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.250 |  Val. Acc: 87.28%
+Epoch: 38 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.267 |  Val. Acc: 87.28%
+Epoch: 39 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.283 |  Val. Acc: 87.25%
+Epoch: 40 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.306 |  Val. Acc: 87.28%
+Epoch: 41 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.324 |  Val. Acc: 87.27%
+Epoch: 42 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.342 |  Val. Acc: 87.21%
+Epoch: 43 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.361 |  Val. Acc: 87.23%
+Epoch: 44 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.377 |  Val. Acc: 87.20%
+Epoch: 45 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.398 |  Val. Acc: 87.19%
+Epoch: 46 | Epoch Time: 0m 7s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.413 |  Val. Acc: 87.17%
+Epoch: 47 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.433 |  Val. Acc: 87.15%
+Epoch: 48 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.449 |  Val. Acc: 87.20%
+Epoch: 49 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.468 |  Val. Acc: 87.17%
+Epoch: 50 | Epoch Time: 0m 6s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.489 |  Val. Acc: 87.11%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 50 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.444 |  Val. Acc: 87.81%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Loss: 0.354 | Test Acc: 86.44%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epoch: 01 | Epoch Time: 0m 16s
+	Train Loss: 0.664 | Train Acc: 58.73%
+	 Val. Loss: 0.590 |  Val. Acc: 68.91%
+Epoch: 02 | Epoch Time: 0m 15s
+	Train Loss: 0.594 | Train Acc: 67.93%
+	 Val. Loss: 0.682 |  Val. Acc: 58.01%
+Epoch: 03 | Epoch Time: 0m 15s
+	Train Loss: 0.545 | Train Acc: 72.32%
+	 Val. Loss: 0.482 |  Val. Acc: 77.54%
+Epoch: 04 | Epoch Time: 0m 15s
+	Train Loss: 0.343 | Train Acc: 85.09%
+	 Val. Loss: 0.359 |  Val. Acc: 85.12%
+Epoch: 05 | Epoch Time: 0m 15s
+	Train Loss: 0.229 | Train Acc: 91.04%
+	 Val. Loss: 0.331 |  Val. Acc: 87.42%
+Epoch: 06 | Epoch Time: 0m 15s
+	Train Loss: 0.156 | Train Acc: 94.39%
+	 Val. Loss: 0.351 |  Val. Acc: 87.56%
+Epoch: 07 | Epoch Time: 0m 14s
+	Train Loss: 0.105 | Train Acc: 96.52%
+	 Val. Loss: 0.394 |  Val. Acc: 87.50%
+Epoch: 08 | Epoch Time: 0m 15s
+	Train Loss: 0.061 | Train Acc: 98.24%
+	 Val. Loss: 0.420 |  Val. Acc: 87.88%
+Epoch: 09 | Epoch Time: 0m 14s
+	Train Loss: 0.043 | Train Acc: 98.77%
+	 Val. Loss: 0.509 |  Val. Acc: 87.94%
+Epoch: 10 | Epoch Time: 0m 15s
+	Train Loss: 0.022 | Train Acc: 99.41%
+	 Val. Loss: 0.538 |  Val. Acc: 87.70%
+Epoch: 11 | Epoch Time: 0m 15s
+	Train Loss: 0.012 | Train Acc: 99.69%
+	 Val. Loss: 0.587 |  Val. Acc: 87.35%
+Epoch: 12 | Epoch Time: 0m 15s
+	Train Loss: 0.007 | Train Acc: 99.87%
+	 Val. Loss: 0.662 |  Val. Acc: 87.62%
+Epoch: 13 | Epoch Time: 0m 15s
+	Train Loss: 0.028 | Train Acc: 99.06%
+	 Val. Loss: 0.580 |  Val. Acc: 87.86%
+Epoch: 14 | Epoch Time: 0m 15s
+	Train Loss: 0.011 | Train Acc: 99.67%
+	 Val. Loss: 0.623 |  Val. Acc: 88.13%
+Epoch: 15 | Epoch Time: 0m 14s
+	Train Loss: 0.007 | Train Acc: 99.80%
+	 Val. Loss: 0.637 |  Val. Acc: 88.00%
+Epoch: 16 | Epoch Time: 0m 15s
+	Train Loss: 0.007 | Train Acc: 99.79%
+	 Val. Loss: 0.731 |  Val. Acc: 85.61%
+Epoch: 17 | Epoch Time: 0m 15s
+	Train Loss: 0.008 | Train Acc: 99.76%
+	 Val. Loss: 0.642 |  Val. Acc: 86.87%
+Epoch: 18 | Epoch Time: 0m 15s
+	Train Loss: 0.005 | Train Acc: 99.87%
+	 Val. Loss: 0.703 |  Val. Acc: 87.42%
+Epoch: 19 | Epoch Time: 0m 15s
+	Train Loss: 0.006 | Train Acc: 99.82%
+	 Val. Loss: 0.748 |  Val. Acc: 87.44%
+Epoch: 20 | Epoch Time: 0m 15s
+	Train Loss: 0.005 | Train Acc: 99.85%
+	 Val. Loss: 0.751 |  Val. Acc: 87.49%
+Epoch: 21 | Epoch Time: 0m 14s
+	Train Loss: 0.001 | Train Acc: 99.96%
+	 Val. Loss: 0.836 |  Val. Acc: 87.60%
+Epoch: 22 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 99.99%
+	 Val. Loss: 0.872 |  Val. Acc: 87.82%
+Epoch: 23 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.921 |  Val. Acc: 87.60%
+Epoch: 24 | Epoch Time: 0m 16s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.950 |  Val. Acc: 87.62%
+Epoch: 25 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.979 |  Val. Acc: 87.58%
+Epoch: 26 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 0.998 |  Val. Acc: 87.69%
+Epoch: 27 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.022 |  Val. Acc: 87.61%
+Epoch: 28 | Epoch Time: 0m 16s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.044 |  Val. Acc: 87.69%
+Epoch: 29 | Epoch Time: 0m 14s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.062 |  Val. Acc: 87.68%
+Epoch: 30 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.082 |  Val. Acc: 87.68%
+Epoch: 31 | Epoch Time: 0m 16s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.099 |  Val. Acc: 87.65%
+Epoch: 32 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.114 |  Val. Acc: 87.62%
+Epoch: 33 | Epoch Time: 0m 14s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.138 |  Val. Acc: 87.69%
+Epoch: 34 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.160 |  Val. Acc: 87.68%
+Epoch: 35 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.178 |  Val. Acc: 87.66%
+Epoch: 36 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.197 |  Val. Acc: 87.62%
+Epoch: 37 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.214 |  Val. Acc: 87.65%
+Epoch: 38 | Epoch Time: 0m 14s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.231 |  Val. Acc: 87.57%
+Epoch: 39 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.246 |  Val. Acc: 87.62%
+Epoch: 40 | Epoch Time: 0m 14s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.261 |  Val. Acc: 87.62%
+Epoch: 41 | Epoch Time: 0m 14s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.283 |  Val. Acc: 87.65%
+Epoch: 42 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.302 |  Val. Acc: 87.64%
+Epoch: 43 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.319 |  Val. Acc: 87.69%
+Epoch: 44 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.337 |  Val. Acc: 87.72%
+Epoch: 45 | Epoch Time: 0m 14s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.360 |  Val. Acc: 87.66%
+Epoch: 46 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.377 |  Val. Acc: 87.80%
+Epoch: 47 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.391 |  Val. Acc: 87.70%
+Epoch: 48 | Epoch Time: 0m 14s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.409 |  Val. Acc: 87.77%
+Epoch: 49 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.426 |  Val. Acc: 87.76%
+Epoch: 50 | Epoch Time: 0m 15s
+	Train Loss: 0.000 | Train Acc: 100.00%
+	 Val. Loss: 1.444 |  Val. Acc: 87.81%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -884,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74C80DB9-EC80-405E-B6FE-50A48B351821}">
-  <dimension ref="A2:D14"/>
+  <dimension ref="A2:D24"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.4140625" style="1" customWidth="1"/>
@@ -1018,6 +2028,98 @@
         <v>23</v>
       </c>
     </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="73.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="71.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="125" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
